--- a/Cowpea_PRESENT.xlsx
+++ b/Cowpea_PRESENT.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INTEL-OMS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\temp\resume\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7E5A1B-0420-4844-907A-6DF1FF25FBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8280" windowHeight="3050" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,12 +18,25 @@
     <sheet name="Sheet4" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="137">
   <si>
     <t>Sl.No.</t>
   </si>
@@ -369,6 +383,9 @@
     <t>181RM-5</t>
   </si>
   <si>
+    <t>Number of seeds germinated out of 100</t>
+  </si>
+  <si>
     <t>Germination percentage%</t>
   </si>
   <si>
@@ -381,10 +398,19 @@
     <t>R3</t>
   </si>
   <si>
+    <t>R4</t>
+  </si>
+  <si>
     <t>Average</t>
   </si>
   <si>
     <t>Seedling length(cm)</t>
+  </si>
+  <si>
+    <t>Average seedling length</t>
+  </si>
+  <si>
+    <t>seedling vigour</t>
   </si>
   <si>
     <t>Shoot</t>
@@ -422,23 +448,11 @@
   <si>
     <t>%*mean seedling length</t>
   </si>
-  <si>
-    <t>Average seedling length</t>
-  </si>
-  <si>
-    <t>seedling vigour</t>
-  </si>
-  <si>
-    <t>Number of seeds germinated out of 100</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -575,8 +589,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -800,22 +816,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AL169"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.81640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.36328125" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" style="15" customWidth="1"/>
     <col min="35" max="35" width="27" style="19" customWidth="1"/>
-    <col min="36" max="36" width="18.90625" style="19" customWidth="1"/>
-    <col min="37" max="37" width="13.453125" style="19" customWidth="1"/>
+    <col min="36" max="36" width="18.88671875" style="19" customWidth="1"/>
+    <col min="37" max="37" width="13.44140625" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -877,7 +893,7 @@
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
     </row>
-    <row r="2" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -979,7 +995,7 @@
       <c r="AK2" s="18"/>
       <c r="AL2" s="2"/>
     </row>
-    <row r="3" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1097,7 +1113,7 @@
       <c r="AK3" s="5"/>
       <c r="AL3" s="4"/>
     </row>
-    <row r="4" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1215,7 +1231,7 @@
       <c r="AK4" s="5"/>
       <c r="AL4" s="4"/>
     </row>
-    <row r="5" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1333,7 +1349,7 @@
       <c r="AK5" s="5"/>
       <c r="AL5" s="4"/>
     </row>
-    <row r="6" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1451,7 +1467,7 @@
       <c r="AK6" s="5"/>
       <c r="AL6" s="4"/>
     </row>
-    <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1567,7 +1583,7 @@
       <c r="AK7" s="8"/>
       <c r="AL7" s="9"/>
     </row>
-    <row r="8" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1683,7 +1699,7 @@
       <c r="AK8" s="5"/>
       <c r="AL8" s="9"/>
     </row>
-    <row r="9" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1799,7 +1815,7 @@
       <c r="AK9" s="5"/>
       <c r="AL9" s="4"/>
     </row>
-    <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1915,7 +1931,7 @@
       <c r="AK10" s="5"/>
       <c r="AL10" s="4"/>
     </row>
-    <row r="11" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -2031,7 +2047,7 @@
       <c r="AK11" s="8"/>
       <c r="AL11" s="9"/>
     </row>
-    <row r="12" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -2147,7 +2163,7 @@
       <c r="AK12" s="8"/>
       <c r="AL12" s="9"/>
     </row>
-    <row r="13" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -2263,7 +2279,7 @@
       <c r="AK13" s="8"/>
       <c r="AL13" s="9"/>
     </row>
-    <row r="14" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -2379,7 +2395,7 @@
       <c r="AK14" s="5"/>
       <c r="AL14" s="4"/>
     </row>
-    <row r="15" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -2495,7 +2511,7 @@
       <c r="AK15" s="5"/>
       <c r="AL15" s="4"/>
     </row>
-    <row r="16" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -2611,7 +2627,7 @@
       <c r="AK16" s="5"/>
       <c r="AL16" s="4"/>
     </row>
-    <row r="17" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -2727,7 +2743,7 @@
       <c r="AK17" s="5"/>
       <c r="AL17" s="4"/>
     </row>
-    <row r="18" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -2843,7 +2859,7 @@
       <c r="AK18" s="5"/>
       <c r="AL18" s="4"/>
     </row>
-    <row r="19" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -2959,7 +2975,7 @@
       <c r="AK19" s="5"/>
       <c r="AL19" s="4"/>
     </row>
-    <row r="20" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -3075,7 +3091,7 @@
       <c r="AK20" s="5"/>
       <c r="AL20" s="4"/>
     </row>
-    <row r="21" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -3191,7 +3207,7 @@
       <c r="AK21" s="5"/>
       <c r="AL21" s="4"/>
     </row>
-    <row r="22" spans="1:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -3307,7 +3323,7 @@
       <c r="AK22" s="8"/>
       <c r="AL22" s="4"/>
     </row>
-    <row r="23" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -3423,7 +3439,7 @@
       <c r="AK23" s="5"/>
       <c r="AL23" s="4"/>
     </row>
-    <row r="24" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -3539,7 +3555,7 @@
       <c r="AK24" s="5"/>
       <c r="AL24" s="4"/>
     </row>
-    <row r="25" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -3655,7 +3671,7 @@
       <c r="AK25" s="5"/>
       <c r="AL25" s="4"/>
     </row>
-    <row r="26" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -3771,7 +3787,7 @@
       <c r="AK26" s="8"/>
       <c r="AL26" s="4"/>
     </row>
-    <row r="27" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -3887,7 +3903,7 @@
       <c r="AK27" s="5"/>
       <c r="AL27" s="4"/>
     </row>
-    <row r="28" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -4003,7 +4019,7 @@
       <c r="AK28" s="5"/>
       <c r="AL28" s="4"/>
     </row>
-    <row r="29" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -4119,7 +4135,7 @@
       <c r="AK29" s="5"/>
       <c r="AL29" s="4"/>
     </row>
-    <row r="30" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -4235,7 +4251,7 @@
       <c r="AK30" s="5"/>
       <c r="AL30" s="4"/>
     </row>
-    <row r="31" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -4351,7 +4367,7 @@
       <c r="AK31" s="5"/>
       <c r="AL31" s="4"/>
     </row>
-    <row r="32" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -4467,7 +4483,7 @@
       <c r="AK32" s="5"/>
       <c r="AL32" s="4"/>
     </row>
-    <row r="33" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -4583,7 +4599,7 @@
       <c r="AK33" s="5"/>
       <c r="AL33" s="4"/>
     </row>
-    <row r="34" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -4699,7 +4715,7 @@
       <c r="AK34" s="5"/>
       <c r="AL34" s="4"/>
     </row>
-    <row r="35" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -4815,7 +4831,7 @@
       <c r="AK35" s="5"/>
       <c r="AL35" s="4"/>
     </row>
-    <row r="36" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -4931,7 +4947,7 @@
       <c r="AK36" s="8"/>
       <c r="AL36" s="9"/>
     </row>
-    <row r="37" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -5047,7 +5063,7 @@
       <c r="AK37" s="8"/>
       <c r="AL37" s="4"/>
     </row>
-    <row r="38" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -5163,7 +5179,7 @@
       <c r="AK38" s="5"/>
       <c r="AL38" s="4"/>
     </row>
-    <row r="39" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -5279,7 +5295,7 @@
       <c r="AK39" s="5"/>
       <c r="AL39" s="4"/>
     </row>
-    <row r="40" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -5395,7 +5411,7 @@
       <c r="AK40" s="5"/>
       <c r="AL40" s="9"/>
     </row>
-    <row r="41" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -5511,7 +5527,7 @@
       <c r="AK41" s="5"/>
       <c r="AL41" s="4"/>
     </row>
-    <row r="42" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -5627,7 +5643,7 @@
       <c r="AK42" s="5"/>
       <c r="AL42" s="4"/>
     </row>
-    <row r="43" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -5743,7 +5759,7 @@
       <c r="AK43" s="8"/>
       <c r="AL43" s="9"/>
     </row>
-    <row r="44" spans="1:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -5859,7 +5875,7 @@
       <c r="AK44" s="8"/>
       <c r="AL44" s="9"/>
     </row>
-    <row r="45" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -5975,7 +5991,7 @@
       <c r="AK45" s="8"/>
       <c r="AL45" s="4"/>
     </row>
-    <row r="46" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -6091,7 +6107,7 @@
       <c r="AK46" s="5"/>
       <c r="AL46" s="4"/>
     </row>
-    <row r="47" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -6207,7 +6223,7 @@
       <c r="AK47" s="5"/>
       <c r="AL47" s="4"/>
     </row>
-    <row r="48" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -6323,7 +6339,7 @@
       <c r="AK48" s="8"/>
       <c r="AL48" s="9"/>
     </row>
-    <row r="49" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -6439,7 +6455,7 @@
       <c r="AK49" s="5"/>
       <c r="AL49" s="4"/>
     </row>
-    <row r="50" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -6555,7 +6571,7 @@
       <c r="AK50" s="5"/>
       <c r="AL50" s="4"/>
     </row>
-    <row r="51" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -6671,7 +6687,7 @@
       <c r="AK51" s="5"/>
       <c r="AL51" s="4"/>
     </row>
-    <row r="52" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>50</v>
       </c>
@@ -6787,7 +6803,7 @@
       <c r="AK52" s="5"/>
       <c r="AL52" s="4"/>
     </row>
-    <row r="53" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>51</v>
       </c>
@@ -6903,7 +6919,7 @@
       <c r="AK53" s="5"/>
       <c r="AL53" s="4"/>
     </row>
-    <row r="54" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -7019,7 +7035,7 @@
       <c r="AK54" s="5"/>
       <c r="AL54" s="4"/>
     </row>
-    <row r="55" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>53</v>
       </c>
@@ -7135,7 +7151,7 @@
       <c r="AK55" s="8"/>
       <c r="AL55" s="4"/>
     </row>
-    <row r="56" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>54</v>
       </c>
@@ -7251,7 +7267,7 @@
       <c r="AK56" s="5"/>
       <c r="AL56" s="4"/>
     </row>
-    <row r="57" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>55</v>
       </c>
@@ -7367,7 +7383,7 @@
       <c r="AK57" s="5"/>
       <c r="AL57" s="4"/>
     </row>
-    <row r="58" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>56</v>
       </c>
@@ -7483,7 +7499,7 @@
       <c r="AK58" s="8"/>
       <c r="AL58" s="9"/>
     </row>
-    <row r="59" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>57</v>
       </c>
@@ -7599,7 +7615,7 @@
       <c r="AK59" s="5"/>
       <c r="AL59" s="4"/>
     </row>
-    <row r="60" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -7715,7 +7731,7 @@
       <c r="AK60" s="8"/>
       <c r="AL60" s="9"/>
     </row>
-    <row r="61" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>59</v>
       </c>
@@ -7831,7 +7847,7 @@
       <c r="AK61" s="5"/>
       <c r="AL61" s="4"/>
     </row>
-    <row r="62" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>60</v>
       </c>
@@ -7947,7 +7963,7 @@
       <c r="AK62" s="5"/>
       <c r="AL62" s="4"/>
     </row>
-    <row r="63" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>61</v>
       </c>
@@ -8063,7 +8079,7 @@
       <c r="AK63" s="5"/>
       <c r="AL63" s="4"/>
     </row>
-    <row r="64" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>62</v>
       </c>
@@ -8179,7 +8195,7 @@
       <c r="AK64" s="5"/>
       <c r="AL64" s="4"/>
     </row>
-    <row r="65" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>63</v>
       </c>
@@ -8295,7 +8311,7 @@
       <c r="AK65" s="8"/>
       <c r="AL65" s="9"/>
     </row>
-    <row r="66" spans="1:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>64</v>
       </c>
@@ -8411,7 +8427,7 @@
       <c r="AK66" s="5"/>
       <c r="AL66" s="4"/>
     </row>
-    <row r="67" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>65</v>
       </c>
@@ -8527,7 +8543,7 @@
       <c r="AK67" s="5"/>
       <c r="AL67" s="4"/>
     </row>
-    <row r="68" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>66</v>
       </c>
@@ -8643,7 +8659,7 @@
       <c r="AK68" s="5"/>
       <c r="AL68" s="4"/>
     </row>
-    <row r="69" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>67</v>
       </c>
@@ -8759,7 +8775,7 @@
       <c r="AK69" s="5"/>
       <c r="AL69" s="4"/>
     </row>
-    <row r="70" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>68</v>
       </c>
@@ -8875,7 +8891,7 @@
       <c r="AK70" s="5"/>
       <c r="AL70" s="4"/>
     </row>
-    <row r="71" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>69</v>
       </c>
@@ -8991,7 +9007,7 @@
       <c r="AK71" s="5"/>
       <c r="AL71" s="4"/>
     </row>
-    <row r="72" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>70</v>
       </c>
@@ -9107,7 +9123,7 @@
       <c r="AK72" s="8"/>
       <c r="AL72" s="4"/>
     </row>
-    <row r="73" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>71</v>
       </c>
@@ -9223,7 +9239,7 @@
       <c r="AK73" s="5"/>
       <c r="AL73" s="4"/>
     </row>
-    <row r="74" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>72</v>
       </c>
@@ -9339,7 +9355,7 @@
       <c r="AK74" s="5"/>
       <c r="AL74" s="4"/>
     </row>
-    <row r="75" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>73</v>
       </c>
@@ -9455,7 +9471,7 @@
       <c r="AK75" s="8"/>
       <c r="AL75" s="9"/>
     </row>
-    <row r="76" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>74</v>
       </c>
@@ -9571,7 +9587,7 @@
       <c r="AK76" s="8"/>
       <c r="AL76" s="9"/>
     </row>
-    <row r="77" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>75</v>
       </c>
@@ -9687,7 +9703,7 @@
       <c r="AK77" s="5"/>
       <c r="AL77" s="4"/>
     </row>
-    <row r="78" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>76</v>
       </c>
@@ -9803,7 +9819,7 @@
       <c r="AK78" s="5"/>
       <c r="AL78" s="9"/>
     </row>
-    <row r="79" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>77</v>
       </c>
@@ -9919,7 +9935,7 @@
       <c r="AK79" s="8"/>
       <c r="AL79" s="9"/>
     </row>
-    <row r="80" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>78</v>
       </c>
@@ -10035,7 +10051,7 @@
       <c r="AK80" s="8"/>
       <c r="AL80" s="9"/>
     </row>
-    <row r="81" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>79</v>
       </c>
@@ -10151,7 +10167,7 @@
       <c r="AK81" s="5"/>
       <c r="AL81" s="4"/>
     </row>
-    <row r="82" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>80</v>
       </c>
@@ -10267,7 +10283,7 @@
       <c r="AK82" s="5"/>
       <c r="AL82" s="4"/>
     </row>
-    <row r="83" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>81</v>
       </c>
@@ -10383,7 +10399,7 @@
       <c r="AK83" s="5"/>
       <c r="AL83" s="4"/>
     </row>
-    <row r="84" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>82</v>
       </c>
@@ -10499,7 +10515,7 @@
       <c r="AK84" s="5"/>
       <c r="AL84" s="4"/>
     </row>
-    <row r="85" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>83</v>
       </c>
@@ -10615,7 +10631,7 @@
       <c r="AK85" s="5"/>
       <c r="AL85" s="4"/>
     </row>
-    <row r="86" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>84</v>
       </c>
@@ -10731,7 +10747,7 @@
       <c r="AK86" s="5"/>
       <c r="AL86" s="4"/>
     </row>
-    <row r="87" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>85</v>
       </c>
@@ -10847,7 +10863,7 @@
       <c r="AK87" s="5"/>
       <c r="AL87" s="4"/>
     </row>
-    <row r="88" spans="1:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>86</v>
       </c>
@@ -10963,7 +10979,7 @@
       <c r="AK88" s="5"/>
       <c r="AL88" s="4"/>
     </row>
-    <row r="89" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>87</v>
       </c>
@@ -11079,7 +11095,7 @@
       <c r="AK89" s="5"/>
       <c r="AL89" s="4"/>
     </row>
-    <row r="90" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>88</v>
       </c>
@@ -11195,7 +11211,7 @@
       <c r="AK90" s="5"/>
       <c r="AL90" s="4"/>
     </row>
-    <row r="91" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>89</v>
       </c>
@@ -11311,7 +11327,7 @@
       <c r="AK91" s="5"/>
       <c r="AL91" s="4"/>
     </row>
-    <row r="92" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>90</v>
       </c>
@@ -11427,7 +11443,7 @@
       <c r="AK92" s="8"/>
       <c r="AL92" s="9"/>
     </row>
-    <row r="93" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>91</v>
       </c>
@@ -11543,7 +11559,7 @@
       <c r="AK93" s="5"/>
       <c r="AL93" s="4"/>
     </row>
-    <row r="94" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>92</v>
       </c>
@@ -11659,7 +11675,7 @@
       <c r="AK94" s="5"/>
       <c r="AL94" s="4"/>
     </row>
-    <row r="95" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>93</v>
       </c>
@@ -11775,7 +11791,7 @@
       <c r="AK95" s="5"/>
       <c r="AL95" s="4"/>
     </row>
-    <row r="96" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>94</v>
       </c>
@@ -11891,7 +11907,7 @@
       <c r="AK96" s="5"/>
       <c r="AL96" s="4"/>
     </row>
-    <row r="97" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>95</v>
       </c>
@@ -12007,7 +12023,7 @@
       <c r="AK97" s="5"/>
       <c r="AL97" s="4"/>
     </row>
-    <row r="98" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>96</v>
       </c>
@@ -12123,7 +12139,7 @@
       <c r="AK98" s="8"/>
       <c r="AL98" s="9"/>
     </row>
-    <row r="99" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>97</v>
       </c>
@@ -12239,7 +12255,7 @@
       <c r="AK99" s="8"/>
       <c r="AL99" s="9"/>
     </row>
-    <row r="100" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>98</v>
       </c>
@@ -12355,7 +12371,7 @@
       <c r="AK100" s="5"/>
       <c r="AL100" s="9"/>
     </row>
-    <row r="101" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>99</v>
       </c>
@@ -12471,7 +12487,7 @@
       <c r="AK101" s="5"/>
       <c r="AL101" s="4"/>
     </row>
-    <row r="102" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>100</v>
       </c>
@@ -12587,7 +12603,7 @@
       <c r="AK102" s="5"/>
       <c r="AL102" s="4"/>
     </row>
-    <row r="103" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>101</v>
       </c>
@@ -12703,7 +12719,7 @@
       <c r="AK103" s="5"/>
       <c r="AL103" s="4"/>
     </row>
-    <row r="104" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>102</v>
       </c>
@@ -12817,7 +12833,7 @@
       <c r="AK104" s="5"/>
       <c r="AL104" s="18"/>
     </row>
-    <row r="105" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>103</v>
       </c>
@@ -12933,7 +12949,7 @@
       <c r="AK105" s="8"/>
       <c r="AL105" s="9"/>
     </row>
-    <row r="106" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>104</v>
       </c>
@@ -13049,7 +13065,7 @@
       <c r="AK106" s="5"/>
       <c r="AL106" s="4"/>
     </row>
-    <row r="107" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>105</v>
       </c>
@@ -13165,7 +13181,7 @@
       <c r="AK107" s="5"/>
       <c r="AL107" s="4"/>
     </row>
-    <row r="108" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>106</v>
       </c>
@@ -13281,7 +13297,7 @@
       <c r="AK108" s="5"/>
       <c r="AL108" s="4"/>
     </row>
-    <row r="109" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>107</v>
       </c>
@@ -13397,7 +13413,7 @@
       <c r="AK109" s="8"/>
       <c r="AL109" s="9"/>
     </row>
-    <row r="110" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>108</v>
       </c>
@@ -13513,7 +13529,7 @@
       <c r="AK110" s="5"/>
       <c r="AL110" s="4"/>
     </row>
-    <row r="111" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>109</v>
       </c>
@@ -13629,7 +13645,7 @@
       <c r="AK111" s="5"/>
       <c r="AL111" s="4"/>
     </row>
-    <row r="112" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>110</v>
       </c>
@@ -13745,7 +13761,7 @@
       <c r="AK112" s="5"/>
       <c r="AL112" s="4"/>
     </row>
-    <row r="113" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>111</v>
       </c>
@@ -13861,7 +13877,7 @@
       <c r="AK113" s="5"/>
       <c r="AL113" s="4"/>
     </row>
-    <row r="114" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>112</v>
       </c>
@@ -13977,7 +13993,7 @@
       <c r="AK114" s="5"/>
       <c r="AL114" s="4"/>
     </row>
-    <row r="115" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>113</v>
       </c>
@@ -14093,7 +14109,7 @@
       <c r="AK115" s="5"/>
       <c r="AL115" s="4"/>
     </row>
-    <row r="116" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>114</v>
       </c>
@@ -14209,7 +14225,7 @@
       <c r="AK116" s="8"/>
       <c r="AL116" s="9"/>
     </row>
-    <row r="117" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>115</v>
       </c>
@@ -14325,7 +14341,7 @@
       <c r="AK117" s="5"/>
       <c r="AL117" s="4"/>
     </row>
-    <row r="118" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>116</v>
       </c>
@@ -14441,7 +14457,7 @@
       <c r="AK118" s="5"/>
       <c r="AL118" s="4"/>
     </row>
-    <row r="119" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>117</v>
       </c>
@@ -14557,7 +14573,7 @@
       <c r="AK119" s="5"/>
       <c r="AL119" s="4"/>
     </row>
-    <row r="120" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>118</v>
       </c>
@@ -14673,7 +14689,7 @@
       <c r="AK120" s="5"/>
       <c r="AL120" s="4"/>
     </row>
-    <row r="121" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>119</v>
       </c>
@@ -14789,7 +14805,7 @@
       <c r="AK121" s="5"/>
       <c r="AL121" s="4"/>
     </row>
-    <row r="122" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>120</v>
       </c>
@@ -14905,7 +14921,7 @@
       <c r="AK122" s="8"/>
       <c r="AL122" s="9"/>
     </row>
-    <row r="123" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>121</v>
       </c>
@@ -15021,7 +15037,7 @@
       <c r="AK123" s="8"/>
       <c r="AL123" s="9"/>
     </row>
-    <row r="124" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>122</v>
       </c>
@@ -15137,7 +15153,7 @@
       <c r="AK124" s="5"/>
       <c r="AL124" s="4"/>
     </row>
-    <row r="125" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>123</v>
       </c>
@@ -15251,7 +15267,7 @@
       <c r="AK125" s="5"/>
       <c r="AL125" s="4"/>
     </row>
-    <row r="126" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>124</v>
       </c>
@@ -15365,7 +15381,7 @@
       <c r="AK126" s="5"/>
       <c r="AL126" s="4"/>
     </row>
-    <row r="127" spans="1:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>125</v>
       </c>
@@ -15479,7 +15495,7 @@
       <c r="AK127" s="5"/>
       <c r="AL127" s="4"/>
     </row>
-    <row r="128" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>126</v>
       </c>
@@ -15593,7 +15609,7 @@
       <c r="AK128" s="5"/>
       <c r="AL128" s="4"/>
     </row>
-    <row r="129" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>127</v>
       </c>
@@ -15707,7 +15723,7 @@
       <c r="AK129" s="5"/>
       <c r="AL129" s="9"/>
     </row>
-    <row r="130" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>128</v>
       </c>
@@ -15823,7 +15839,7 @@
       <c r="AK130" s="8"/>
       <c r="AL130" s="9"/>
     </row>
-    <row r="131" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>129</v>
       </c>
@@ -15850,7 +15866,7 @@
         <v>65.099999999999994</v>
       </c>
       <c r="J131" s="6">
-        <f t="shared" ref="J131:J134" si="24">AVERAGE(E131:I131)</f>
+        <f t="shared" ref="J131:J162" si="24">AVERAGE(E131:I131)</f>
         <v>59.98</v>
       </c>
       <c r="K131" s="6">
@@ -15869,7 +15885,7 @@
         <v>8</v>
       </c>
       <c r="P131" s="6">
-        <f t="shared" ref="P131:P134" si="25">AVERAGE(K131:O131)</f>
+        <f t="shared" ref="P131:P162" si="25">AVERAGE(K131:O131)</f>
         <v>8</v>
       </c>
       <c r="Q131" s="6">
@@ -15888,7 +15904,7 @@
         <v>12</v>
       </c>
       <c r="V131" s="3">
-        <f t="shared" ref="V131:V134" si="26">AVERAGE(Q131:U131)</f>
+        <f t="shared" ref="V131:V162" si="26">AVERAGE(Q131:U131)</f>
         <v>12.8</v>
       </c>
       <c r="W131" s="6">
@@ -15907,7 +15923,7 @@
         <v>17</v>
       </c>
       <c r="AB131" s="3">
-        <f t="shared" ref="AB131:AB134" si="27">AVERAGE(W131:AA131)</f>
+        <f t="shared" ref="AB131:AB162" si="27">AVERAGE(W131:AA131)</f>
         <v>16.8</v>
       </c>
       <c r="AC131" s="6">
@@ -15926,20 +15942,20 @@
         <v>14.5</v>
       </c>
       <c r="AH131" s="3">
-        <f t="shared" ref="AH131:AH134" si="28">AVERAGE(AC131:AG131)</f>
+        <f t="shared" ref="AH131:AH162" si="28">AVERAGE(AC131:AG131)</f>
         <v>14.6</v>
       </c>
       <c r="AI131" s="7">
         <v>59.42</v>
       </c>
       <c r="AJ131" s="4">
-        <f t="shared" ref="AJ131:AJ134" si="29">AI131*7407.4/1000</f>
+        <f t="shared" ref="AJ131:AJ162" si="29">AI131*7407.4/1000</f>
         <v>440.14770799999997</v>
       </c>
       <c r="AK131" s="5"/>
       <c r="AL131" s="4"/>
     </row>
-    <row r="132" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>130</v>
       </c>
@@ -16055,7 +16071,7 @@
       <c r="AK132" s="5"/>
       <c r="AL132" s="4"/>
     </row>
-    <row r="133" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>131</v>
       </c>
@@ -16171,7 +16187,7 @@
       <c r="AK133" s="5"/>
       <c r="AL133" s="4"/>
     </row>
-    <row r="134" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>132</v>
       </c>
@@ -16287,7 +16303,7 @@
       <c r="AK134" s="5"/>
       <c r="AL134" s="4"/>
     </row>
-    <row r="136" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -16327,7 +16343,7 @@
       <c r="AK136" s="2"/>
       <c r="AL136" s="9"/>
     </row>
-    <row r="137" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -16367,7 +16383,7 @@
       <c r="AK137" s="2"/>
       <c r="AL137" s="2"/>
     </row>
-    <row r="138" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -16407,97 +16423,97 @@
       <c r="AK138" s="2"/>
       <c r="AL138" s="2"/>
     </row>
-    <row r="139" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ139" s="18"/>
     </row>
-    <row r="140" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ140" s="18"/>
     </row>
-    <row r="141" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ141" s="18"/>
     </row>
-    <row r="142" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ142" s="18"/>
     </row>
-    <row r="143" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ143" s="18"/>
     </row>
-    <row r="144" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ144" s="18"/>
     </row>
-    <row r="145" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ145" s="18"/>
     </row>
-    <row r="146" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ146" s="18"/>
     </row>
-    <row r="147" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ147" s="18"/>
     </row>
-    <row r="148" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ148" s="18"/>
     </row>
-    <row r="149" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ149" s="18"/>
     </row>
-    <row r="150" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ150" s="18"/>
     </row>
-    <row r="151" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ151" s="18"/>
     </row>
-    <row r="152" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ152" s="18"/>
     </row>
-    <row r="153" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ153" s="18"/>
     </row>
-    <row r="154" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ154" s="18"/>
     </row>
-    <row r="155" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ155" s="18"/>
     </row>
-    <row r="156" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ156" s="18"/>
     </row>
-    <row r="157" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ157" s="18"/>
     </row>
-    <row r="158" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ158" s="18"/>
     </row>
-    <row r="159" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ159" s="18"/>
     </row>
-    <row r="160" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ160" s="18"/>
     </row>
-    <row r="161" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ161" s="18"/>
     </row>
-    <row r="162" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ162" s="18"/>
     </row>
-    <row r="163" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ163" s="18"/>
     </row>
-    <row r="164" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ164" s="18"/>
     </row>
-    <row r="165" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ165" s="18"/>
     </row>
-    <row r="166" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ166" s="18"/>
     </row>
-    <row r="167" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ167" s="18"/>
     </row>
-    <row r="168" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ168" s="18"/>
     </row>
-    <row r="169" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="36:36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AJ169" s="18"/>
     </row>
   </sheetData>
@@ -16509,21 +16525,21 @@
     <mergeCell ref="W1:AA1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1"/>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="8.90625" style="19"/>
-    <col min="5" max="5" width="8.7265625" style="21"/>
-    <col min="6" max="6" width="10.36328125" style="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.1796875" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="8.88671875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" style="19" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" style="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -16531,27 +16547,27 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="G1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2" s="19" t="s">
+      <c r="B2" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="C2" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>136</v>
+      <c r="D2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" t="s">
+        <v>120</v>
       </c>
       <c r="F2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H2" s="17"/>
     </row>
@@ -16559,24 +16575,24 @@
       <c r="A4">
         <v>7</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4">
         <v>90</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4">
         <v>84</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4">
         <v>92</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4">
         <v>86</v>
       </c>
       <c r="F4" s="16">
-        <f>AVERAGE(B4:E4)</f>
+        <f t="shared" ref="F4:F18" si="0">AVERAGE(B4:E4)</f>
         <v>88</v>
       </c>
       <c r="G4" s="16">
-        <f>F4/100*100</f>
+        <f t="shared" ref="G4:G18" si="1">F4/100*100</f>
         <v>88</v>
       </c>
     </row>
@@ -16584,24 +16600,24 @@
       <c r="A5">
         <v>13</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5">
         <v>100</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5">
         <v>96</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5">
         <v>98</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5">
         <v>95</v>
       </c>
       <c r="F5" s="16">
-        <f t="shared" ref="F5:F18" si="0">AVERAGE(B5:E5)</f>
+        <f t="shared" si="0"/>
         <v>97.25</v>
       </c>
       <c r="G5" s="16">
-        <f t="shared" ref="G5:G18" si="1">F5/100*100</f>
+        <f t="shared" si="1"/>
         <v>97.25</v>
       </c>
     </row>
@@ -16609,16 +16625,16 @@
       <c r="A6">
         <v>14</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6">
         <v>84</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6">
         <v>90</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6">
         <v>92</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6">
         <v>86</v>
       </c>
       <c r="F6" s="16">
@@ -16634,16 +16650,16 @@
       <c r="A7">
         <v>18</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7">
         <v>84</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7">
         <v>88</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7">
         <v>92</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7">
         <v>87</v>
       </c>
       <c r="F7" s="16">
@@ -16659,16 +16675,16 @@
       <c r="A8">
         <v>19</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8">
         <v>94</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8">
         <v>98</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8">
         <v>90</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8">
         <v>95</v>
       </c>
       <c r="F8" s="16">
@@ -16684,16 +16700,16 @@
       <c r="A9">
         <v>36</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9">
         <v>92</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9">
         <v>94</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9">
         <v>88</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9">
         <v>90</v>
       </c>
       <c r="F9" s="16">
@@ -16709,16 +16725,16 @@
       <c r="A10">
         <v>43</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10">
         <v>96</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10">
         <v>94</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10">
         <v>92</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10">
         <v>91</v>
       </c>
       <c r="F10" s="16">
@@ -16734,16 +16750,16 @@
       <c r="A11">
         <v>45</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11">
         <v>82</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11">
         <v>90</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11">
         <v>88</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11">
         <v>86</v>
       </c>
       <c r="F11" s="16">
@@ -16759,16 +16775,16 @@
       <c r="A12">
         <v>48</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12">
         <v>92</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12">
         <v>96</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12">
         <v>94</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12">
         <v>95</v>
       </c>
       <c r="F12" s="16">
@@ -16784,16 +16800,16 @@
       <c r="A13">
         <v>49</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13">
         <v>88</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13">
         <v>92</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13">
         <v>96</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13">
         <v>91</v>
       </c>
       <c r="F13" s="16">
@@ -16809,16 +16825,16 @@
       <c r="A14">
         <v>53</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14">
         <v>94</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14">
         <v>96</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14">
         <v>94</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14">
         <v>93</v>
       </c>
       <c r="F14" s="16">
@@ -16834,16 +16850,16 @@
       <c r="A15">
         <v>58</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15">
         <v>96</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15">
         <v>98</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15">
         <v>96</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15">
         <v>97</v>
       </c>
       <c r="F15" s="16">
@@ -16859,16 +16875,16 @@
       <c r="A16">
         <v>78</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16">
         <v>92</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16">
         <v>88</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16">
         <v>92</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16">
         <v>86</v>
       </c>
       <c r="F16" s="16">
@@ -16884,16 +16900,16 @@
       <c r="A17">
         <v>89</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17">
         <v>90</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17">
         <v>84</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17">
         <v>94</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17">
         <v>92</v>
       </c>
       <c r="F17" s="16">
@@ -16909,16 +16925,16 @@
       <c r="A18">
         <v>112</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18">
         <v>86</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18">
         <v>94</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18">
         <v>92</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18">
         <v>90</v>
       </c>
       <c r="F18" s="16">
@@ -16936,21 +16952,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL33"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:AV33"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="19" customWidth="1"/>
-    <col min="13" max="15" width="8.7265625" style="21"/>
-    <col min="26" max="28" width="8.7265625" style="22"/>
+    <col min="1" max="1" width="8.77734375" style="19" customWidth="1"/>
+    <col min="13" max="15" width="8.77734375" style="19" customWidth="1"/>
+    <col min="26" max="28" width="8.77734375" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="24"/>
@@ -16975,9 +16991,9 @@
       <c r="X1" s="24"/>
       <c r="Y1" s="24"/>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C2" s="25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="24"/>
@@ -16989,7 +17005,7 @@
       <c r="K2" s="24"/>
       <c r="L2" s="24"/>
       <c r="P2" s="25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q2" s="24"/>
       <c r="R2" s="24"/>
@@ -17001,7 +17017,7 @@
       <c r="X2" s="24"/>
       <c r="Y2" s="24"/>
       <c r="AC2" s="25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AD2" s="24"/>
       <c r="AE2" s="24"/>
@@ -17012,8 +17028,11 @@
       <c r="AJ2" s="24"/>
       <c r="AK2" s="24"/>
       <c r="AL2" s="24"/>
-    </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM2" s="21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C3">
         <v>1</v>
       </c>
@@ -17044,11 +17063,11 @@
       <c r="L3">
         <v>10</v>
       </c>
-      <c r="N3" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>134</v>
+      <c r="N3" t="s">
+        <v>123</v>
+      </c>
+      <c r="O3" t="s">
+        <v>124</v>
       </c>
       <c r="P3">
         <v>1</v>
@@ -17110,10 +17129,40 @@
       <c r="AL3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM3" s="22">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="22">
+        <v>2</v>
+      </c>
+      <c r="AO3" s="22">
+        <v>3</v>
+      </c>
+      <c r="AP3" s="22">
+        <v>4</v>
+      </c>
+      <c r="AQ3" s="22">
+        <v>5</v>
+      </c>
+      <c r="AR3" s="22">
+        <v>6</v>
+      </c>
+      <c r="AS3" s="22">
+        <v>7</v>
+      </c>
+      <c r="AT3" s="22">
+        <v>8</v>
+      </c>
+      <c r="AU3" s="22">
+        <v>9</v>
+      </c>
+      <c r="AV3" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -17148,15 +17197,15 @@
       <c r="L4">
         <v>15.6</v>
       </c>
-      <c r="M4" s="21">
-        <f>AVERAGE(C4:L4)</f>
+      <c r="M4">
+        <f t="shared" ref="M4:M33" si="0">AVERAGE(C4:L4)</f>
         <v>16.119999999999997</v>
       </c>
-      <c r="N4" s="21">
+      <c r="N4">
         <f>AVERAGE(C4:L4)+AVERAGE(C5:L5)</f>
         <v>26.97</v>
       </c>
-      <c r="O4" s="21">
+      <c r="O4">
         <f>26.97*88.7</f>
         <v>2392.239</v>
       </c>
@@ -17220,10 +17269,40 @@
       <c r="AL4">
         <v>14.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM4">
+        <v>13.5</v>
+      </c>
+      <c r="AN4">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="AO4">
+        <v>15.6</v>
+      </c>
+      <c r="AP4">
+        <v>17.8</v>
+      </c>
+      <c r="AQ4">
+        <v>16</v>
+      </c>
+      <c r="AR4">
+        <v>14.3</v>
+      </c>
+      <c r="AS4">
+        <v>13.2</v>
+      </c>
+      <c r="AT4">
+        <v>16.5</v>
+      </c>
+      <c r="AU4">
+        <v>15.1</v>
+      </c>
+      <c r="AV4">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C5">
         <v>11.6</v>
@@ -17255,8 +17334,8 @@
       <c r="L5">
         <v>9.1999999999999993</v>
       </c>
-      <c r="M5" s="21">
-        <f t="shared" ref="M5:M33" si="0">AVERAGE(C5:L5)</f>
+      <c r="M5">
+        <f t="shared" si="0"/>
         <v>10.85</v>
       </c>
       <c r="P5">
@@ -17319,10 +17398,40 @@
       <c r="AL5">
         <v>11.2</v>
       </c>
-    </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM5">
+        <v>8.6</v>
+      </c>
+      <c r="AN5">
+        <v>12.5</v>
+      </c>
+      <c r="AO5">
+        <v>12</v>
+      </c>
+      <c r="AP5">
+        <v>11.6</v>
+      </c>
+      <c r="AQ5">
+        <v>12.2</v>
+      </c>
+      <c r="AR5">
+        <v>9.6</v>
+      </c>
+      <c r="AS5">
+        <v>14</v>
+      </c>
+      <c r="AT5">
+        <v>10.9</v>
+      </c>
+      <c r="AU5">
+        <v>11.8</v>
+      </c>
+      <c r="AV5">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B6">
         <v>13</v>
@@ -17357,15 +17466,15 @@
       <c r="L6">
         <v>22</v>
       </c>
-      <c r="M6" s="21">
+      <c r="M6">
         <f t="shared" si="0"/>
         <v>18.7</v>
       </c>
-      <c r="N6" s="21">
+      <c r="N6">
         <f>AVERAGE(C6:L6)+AVERAGE(C7:L7)</f>
         <v>29.5</v>
       </c>
-      <c r="O6" s="21">
+      <c r="O6">
         <f>29.5*98</f>
         <v>2891</v>
       </c>
@@ -17429,10 +17538,40 @@
       <c r="AL6">
         <v>14.1</v>
       </c>
-    </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM6">
+        <v>20.8</v>
+      </c>
+      <c r="AN6">
+        <v>15.7</v>
+      </c>
+      <c r="AO6">
+        <v>10.1</v>
+      </c>
+      <c r="AP6">
+        <v>14.4</v>
+      </c>
+      <c r="AQ6">
+        <v>24.1</v>
+      </c>
+      <c r="AR6">
+        <v>14.7</v>
+      </c>
+      <c r="AS6">
+        <v>11</v>
+      </c>
+      <c r="AT6">
+        <v>15</v>
+      </c>
+      <c r="AU6">
+        <v>16.7</v>
+      </c>
+      <c r="AV6">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -17464,7 +17603,7 @@
       <c r="L7">
         <v>7</v>
       </c>
-      <c r="M7" s="21">
+      <c r="M7">
         <f t="shared" si="0"/>
         <v>10.8</v>
       </c>
@@ -17528,10 +17667,40 @@
       <c r="AL7">
         <v>13.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM7">
+        <v>13.2</v>
+      </c>
+      <c r="AN7">
+        <v>12.8</v>
+      </c>
+      <c r="AO7">
+        <v>11.6</v>
+      </c>
+      <c r="AP7">
+        <v>11.5</v>
+      </c>
+      <c r="AQ7">
+        <v>11.8</v>
+      </c>
+      <c r="AR7">
+        <v>11</v>
+      </c>
+      <c r="AS7">
+        <v>11.6</v>
+      </c>
+      <c r="AT7">
+        <v>11.8</v>
+      </c>
+      <c r="AU7">
+        <v>13.6</v>
+      </c>
+      <c r="AV7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B8">
         <v>14</v>
@@ -17566,15 +17735,15 @@
       <c r="L8">
         <v>16.600000000000001</v>
       </c>
-      <c r="M8" s="21">
+      <c r="M8">
         <f t="shared" si="0"/>
         <v>14.3</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8">
         <f>AVERAGE(C8:L8)+AVERAGE(C9:L9)</f>
         <v>28.43</v>
       </c>
-      <c r="O8" s="21">
+      <c r="O8">
         <f>28.43*88.7</f>
         <v>2521.741</v>
       </c>
@@ -17638,10 +17807,40 @@
       <c r="AL8">
         <v>11.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM8">
+        <v>21.3</v>
+      </c>
+      <c r="AN8">
+        <v>14.7</v>
+      </c>
+      <c r="AO8">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="AP8">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="AQ8">
+        <v>16.5</v>
+      </c>
+      <c r="AR8">
+        <v>15.7</v>
+      </c>
+      <c r="AS8">
+        <v>14.3</v>
+      </c>
+      <c r="AT8">
+        <v>11.2</v>
+      </c>
+      <c r="AU8">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="AV8">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C9">
         <v>11.5</v>
@@ -17673,7 +17872,7 @@
       <c r="L9">
         <v>10.8</v>
       </c>
-      <c r="M9" s="21">
+      <c r="M9">
         <f t="shared" si="0"/>
         <v>14.13</v>
       </c>
@@ -17737,10 +17936,40 @@
       <c r="AL9">
         <v>14.8</v>
       </c>
-    </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM9">
+        <v>15.6</v>
+      </c>
+      <c r="AN9">
+        <v>12.6</v>
+      </c>
+      <c r="AO9">
+        <v>15</v>
+      </c>
+      <c r="AP9">
+        <v>15.3</v>
+      </c>
+      <c r="AQ9">
+        <v>15.3</v>
+      </c>
+      <c r="AR9">
+        <v>13.5</v>
+      </c>
+      <c r="AS9">
+        <v>14.7</v>
+      </c>
+      <c r="AT9">
+        <v>14.5</v>
+      </c>
+      <c r="AU9">
+        <v>12.9</v>
+      </c>
+      <c r="AV9">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B10">
         <v>18</v>
@@ -17775,15 +18004,15 @@
       <c r="L10">
         <v>17.100000000000001</v>
       </c>
-      <c r="M10" s="21">
+      <c r="M10">
         <f t="shared" si="0"/>
         <v>17.84</v>
       </c>
-      <c r="N10" s="21">
+      <c r="N10">
         <f>AVERAGE(C10:L10)+AVERAGE(C11:L11)</f>
         <v>30.05</v>
       </c>
-      <c r="O10" s="21">
+      <c r="O10">
         <f>30.05*88</f>
         <v>2644.4</v>
       </c>
@@ -17847,10 +18076,40 @@
       <c r="AL10">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM10">
+        <v>15.1</v>
+      </c>
+      <c r="AN10">
+        <v>17.3</v>
+      </c>
+      <c r="AO10">
+        <v>16.5</v>
+      </c>
+      <c r="AP10">
+        <v>15.8</v>
+      </c>
+      <c r="AQ10">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="AR10">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="AS10">
+        <v>16.5</v>
+      </c>
+      <c r="AT10">
+        <v>16.7</v>
+      </c>
+      <c r="AU10">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="AV10">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C11">
         <v>12</v>
@@ -17882,7 +18141,7 @@
       <c r="L11">
         <v>11.9</v>
       </c>
-      <c r="M11" s="21">
+      <c r="M11">
         <f t="shared" si="0"/>
         <v>12.21</v>
       </c>
@@ -17946,10 +18205,40 @@
       <c r="AL11">
         <v>12.6</v>
       </c>
-    </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM11">
+        <v>12</v>
+      </c>
+      <c r="AN11">
+        <v>12.8</v>
+      </c>
+      <c r="AO11">
+        <v>12.1</v>
+      </c>
+      <c r="AP11">
+        <v>13.2</v>
+      </c>
+      <c r="AQ11">
+        <v>13.7</v>
+      </c>
+      <c r="AR11">
+        <v>10.4</v>
+      </c>
+      <c r="AS11">
+        <v>14.1</v>
+      </c>
+      <c r="AT11">
+        <v>13.8</v>
+      </c>
+      <c r="AU11">
+        <v>11.2</v>
+      </c>
+      <c r="AV11">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B12">
         <v>19</v>
@@ -17984,15 +18273,15 @@
       <c r="L12">
         <v>19.8</v>
       </c>
-      <c r="M12" s="21">
+      <c r="M12">
         <f t="shared" si="0"/>
         <v>18.380000000000003</v>
       </c>
-      <c r="N12" s="21">
+      <c r="N12">
         <f>AVERAGE(C12:L12)+AVERAGE(C13:L13)</f>
         <v>32.980000000000004</v>
       </c>
-      <c r="O12" s="21">
+      <c r="O12">
         <f>32.98*94</f>
         <v>3100.12</v>
       </c>
@@ -18056,10 +18345,40 @@
       <c r="AL12">
         <v>16.8</v>
       </c>
-    </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM12">
+        <v>19</v>
+      </c>
+      <c r="AN12">
+        <v>21.9</v>
+      </c>
+      <c r="AO12">
+        <v>16.2</v>
+      </c>
+      <c r="AP12">
+        <v>15</v>
+      </c>
+      <c r="AQ12">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AR12">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="AS12">
+        <v>18.7</v>
+      </c>
+      <c r="AT12">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="AU12">
+        <v>21.9</v>
+      </c>
+      <c r="AV12">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C13">
         <v>16</v>
@@ -18091,7 +18410,7 @@
       <c r="L13">
         <v>12.6</v>
       </c>
-      <c r="M13" s="21">
+      <c r="M13">
         <f t="shared" si="0"/>
         <v>14.599999999999998</v>
       </c>
@@ -18155,10 +18474,40 @@
       <c r="AL13">
         <v>14.6</v>
       </c>
-    </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM13">
+        <v>14.9</v>
+      </c>
+      <c r="AN13">
+        <v>14.2</v>
+      </c>
+      <c r="AO13">
+        <v>14.1</v>
+      </c>
+      <c r="AP13">
+        <v>11.4</v>
+      </c>
+      <c r="AQ13">
+        <v>15.7</v>
+      </c>
+      <c r="AR13">
+        <v>15.6</v>
+      </c>
+      <c r="AS13">
+        <v>13.7</v>
+      </c>
+      <c r="AT13">
+        <v>20</v>
+      </c>
+      <c r="AU13">
+        <v>11.8</v>
+      </c>
+      <c r="AV13">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B14">
         <v>36</v>
@@ -18193,15 +18542,15 @@
       <c r="L14">
         <v>11</v>
       </c>
-      <c r="M14" s="21">
+      <c r="M14">
         <f t="shared" si="0"/>
         <v>10.4</v>
       </c>
-      <c r="N14" s="21">
+      <c r="N14">
         <f>AVERAGE(C14:L14)+AVERAGE(C15:L15)</f>
         <v>23.9</v>
       </c>
-      <c r="O14" s="21">
+      <c r="O14">
         <f>23.9*91</f>
         <v>2174.9</v>
       </c>
@@ -18265,10 +18614,40 @@
       <c r="AL14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM14">
+        <v>7.7</v>
+      </c>
+      <c r="AN14">
+        <v>6.7</v>
+      </c>
+      <c r="AO14">
+        <v>13.6</v>
+      </c>
+      <c r="AP14">
+        <v>8.5</v>
+      </c>
+      <c r="AQ14">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AR14">
+        <v>9.1</v>
+      </c>
+      <c r="AS14">
+        <v>11.7</v>
+      </c>
+      <c r="AT14">
+        <v>14.1</v>
+      </c>
+      <c r="AU14">
+        <v>11.5</v>
+      </c>
+      <c r="AV14">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -18300,7 +18679,7 @@
       <c r="L15">
         <v>13</v>
       </c>
-      <c r="M15" s="21">
+      <c r="M15">
         <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
@@ -18364,10 +18743,40 @@
       <c r="AL15">
         <v>14.4</v>
       </c>
-    </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM15">
+        <v>13.3</v>
+      </c>
+      <c r="AN15">
+        <v>14</v>
+      </c>
+      <c r="AO15">
+        <v>14.6</v>
+      </c>
+      <c r="AP15">
+        <v>14.4</v>
+      </c>
+      <c r="AQ15">
+        <v>13.8</v>
+      </c>
+      <c r="AR15">
+        <v>15.2</v>
+      </c>
+      <c r="AS15">
+        <v>13.5</v>
+      </c>
+      <c r="AT15">
+        <v>13.5</v>
+      </c>
+      <c r="AU15">
+        <v>14.1</v>
+      </c>
+      <c r="AV15">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B16">
         <v>43</v>
@@ -18402,15 +18811,15 @@
       <c r="L16">
         <v>16.8</v>
       </c>
-      <c r="M16" s="21">
+      <c r="M16">
         <f t="shared" si="0"/>
         <v>17.18</v>
       </c>
-      <c r="N16" s="21">
+      <c r="N16">
         <f>AVERAGE(C16:L16)+AVERAGE(C17:L17)</f>
         <v>32.36</v>
       </c>
-      <c r="O16" s="21">
+      <c r="O16">
         <f>32.36*94</f>
         <v>3041.84</v>
       </c>
@@ -18474,10 +18883,40 @@
       <c r="AL16">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM16">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="AN16">
+        <v>17.3</v>
+      </c>
+      <c r="AO16">
+        <v>19.8</v>
+      </c>
+      <c r="AP16">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="AQ16">
+        <v>14.1</v>
+      </c>
+      <c r="AR16">
+        <v>18.8</v>
+      </c>
+      <c r="AS16">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="AT16">
+        <v>18</v>
+      </c>
+      <c r="AU16">
+        <v>19</v>
+      </c>
+      <c r="AV16">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C17">
         <v>17.5</v>
@@ -18509,7 +18948,7 @@
       <c r="L17">
         <v>12.5</v>
       </c>
-      <c r="M17" s="21">
+      <c r="M17">
         <f t="shared" si="0"/>
         <v>15.180000000000001</v>
       </c>
@@ -18573,10 +19012,40 @@
       <c r="AL17">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM17">
+        <v>15.2</v>
+      </c>
+      <c r="AN17">
+        <v>14.6</v>
+      </c>
+      <c r="AO17">
+        <v>14.2</v>
+      </c>
+      <c r="AP17">
+        <v>15.9</v>
+      </c>
+      <c r="AQ17">
+        <v>14.9</v>
+      </c>
+      <c r="AR17">
+        <v>16.2</v>
+      </c>
+      <c r="AS17">
+        <v>16.5</v>
+      </c>
+      <c r="AT17">
+        <v>13.8</v>
+      </c>
+      <c r="AU17">
+        <v>14.1</v>
+      </c>
+      <c r="AV17">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B18">
         <v>45</v>
@@ -18611,15 +19080,15 @@
       <c r="L18">
         <v>14.2</v>
       </c>
-      <c r="M18" s="21">
+      <c r="M18">
         <f t="shared" si="0"/>
         <v>16.72</v>
       </c>
-      <c r="N18" s="21">
+      <c r="N18">
         <f>AVERAGE(C18:L18)+AVERAGE(C19:L19)</f>
         <v>32.21</v>
       </c>
-      <c r="O18" s="21">
+      <c r="O18">
         <f>32.21*86.7</f>
         <v>2792.607</v>
       </c>
@@ -18683,10 +19152,40 @@
       <c r="AL18">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM18">
+        <v>16</v>
+      </c>
+      <c r="AN18">
+        <v>20.5</v>
+      </c>
+      <c r="AO18">
+        <v>20.7</v>
+      </c>
+      <c r="AP18">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="AQ18">
+        <v>15.6</v>
+      </c>
+      <c r="AR18">
+        <v>14.6</v>
+      </c>
+      <c r="AS18">
+        <v>12</v>
+      </c>
+      <c r="AT18">
+        <v>9.9</v>
+      </c>
+      <c r="AU18">
+        <v>9</v>
+      </c>
+      <c r="AV18">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C19">
         <v>17</v>
@@ -18718,7 +19217,7 @@
       <c r="L19">
         <v>16.600000000000001</v>
       </c>
-      <c r="M19" s="21">
+      <c r="M19">
         <f t="shared" si="0"/>
         <v>15.49</v>
       </c>
@@ -18782,10 +19281,40 @@
       <c r="AL19">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM19">
+        <v>15.1</v>
+      </c>
+      <c r="AN19">
+        <v>14.2</v>
+      </c>
+      <c r="AO19">
+        <v>16</v>
+      </c>
+      <c r="AP19">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="AQ19">
+        <v>13.5</v>
+      </c>
+      <c r="AR19">
+        <v>13.8</v>
+      </c>
+      <c r="AS19">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AT19">
+        <v>13.3</v>
+      </c>
+      <c r="AU19">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="AV19">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B20">
         <v>48</v>
@@ -18820,15 +19349,15 @@
       <c r="L20">
         <v>15</v>
       </c>
-      <c r="M20" s="21">
+      <c r="M20">
         <f t="shared" si="0"/>
         <v>17.5</v>
       </c>
-      <c r="N20" s="21">
+      <c r="N20">
         <f>AVERAGE(C20:L20)+AVERAGE(C21:L21)</f>
         <v>28.8</v>
       </c>
-      <c r="O20" s="21">
+      <c r="O20">
         <f>28.8*94</f>
         <v>2707.2000000000003</v>
       </c>
@@ -18892,10 +19421,40 @@
       <c r="AL20">
         <v>13.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM20">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="AN20">
+        <v>18.2</v>
+      </c>
+      <c r="AO20">
+        <v>13.9</v>
+      </c>
+      <c r="AP20">
+        <v>22.5</v>
+      </c>
+      <c r="AQ20">
+        <v>11.6</v>
+      </c>
+      <c r="AR20">
+        <v>17</v>
+      </c>
+      <c r="AS20">
+        <v>16.2</v>
+      </c>
+      <c r="AT20">
+        <v>22.4</v>
+      </c>
+      <c r="AU20">
+        <v>17.3</v>
+      </c>
+      <c r="AV20">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C21">
         <v>10</v>
@@ -18927,7 +19486,7 @@
       <c r="L21">
         <v>12</v>
       </c>
-      <c r="M21" s="21">
+      <c r="M21">
         <f t="shared" si="0"/>
         <v>11.3</v>
       </c>
@@ -18991,10 +19550,40 @@
       <c r="AL21">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM21">
+        <v>12</v>
+      </c>
+      <c r="AN21">
+        <v>14</v>
+      </c>
+      <c r="AO21">
+        <v>10</v>
+      </c>
+      <c r="AP21">
+        <v>13</v>
+      </c>
+      <c r="AQ21">
+        <v>13</v>
+      </c>
+      <c r="AR21">
+        <v>11</v>
+      </c>
+      <c r="AS21">
+        <v>11</v>
+      </c>
+      <c r="AT21">
+        <v>11</v>
+      </c>
+      <c r="AU21">
+        <v>13</v>
+      </c>
+      <c r="AV21">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B22">
         <v>49</v>
@@ -19029,15 +19618,15 @@
       <c r="L22">
         <v>14.4</v>
       </c>
-      <c r="M22" s="21">
+      <c r="M22">
         <f t="shared" si="0"/>
         <v>17.330000000000002</v>
       </c>
-      <c r="N22" s="21">
+      <c r="N22">
         <f>AVERAGE(C22:L22)+AVERAGE(C23:L23)</f>
         <v>29.380000000000003</v>
       </c>
-      <c r="O22" s="21">
+      <c r="O22">
         <f>29.38*92</f>
         <v>2702.96</v>
       </c>
@@ -19101,10 +19690,40 @@
       <c r="AL22">
         <v>20.399999999999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM22">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="AN22">
+        <v>21.3</v>
+      </c>
+      <c r="AO22">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="AP22">
+        <v>21</v>
+      </c>
+      <c r="AQ22">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="AR22">
+        <v>16.3</v>
+      </c>
+      <c r="AS22">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AT22">
+        <v>18.3</v>
+      </c>
+      <c r="AU22">
+        <v>11</v>
+      </c>
+      <c r="AV22">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C23">
         <v>14.4</v>
@@ -19136,7 +19755,7 @@
       <c r="L23">
         <v>11.1</v>
       </c>
-      <c r="M23" s="21">
+      <c r="M23">
         <f t="shared" si="0"/>
         <v>12.05</v>
       </c>
@@ -19200,10 +19819,40 @@
       <c r="AL23">
         <v>13.7</v>
       </c>
-    </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM23">
+        <v>13.5</v>
+      </c>
+      <c r="AN23">
+        <v>14.2</v>
+      </c>
+      <c r="AO23">
+        <v>14.5</v>
+      </c>
+      <c r="AP23">
+        <v>10.6</v>
+      </c>
+      <c r="AQ23">
+        <v>12.9</v>
+      </c>
+      <c r="AR23">
+        <v>11.5</v>
+      </c>
+      <c r="AS23">
+        <v>11.3</v>
+      </c>
+      <c r="AT23">
+        <v>12.1</v>
+      </c>
+      <c r="AU23">
+        <v>11.3</v>
+      </c>
+      <c r="AV23">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B24">
         <v>53</v>
@@ -19238,15 +19887,15 @@
       <c r="L24">
         <v>17.3</v>
       </c>
-      <c r="M24" s="21">
+      <c r="M24">
         <f t="shared" si="0"/>
         <v>17.360000000000003</v>
       </c>
-      <c r="N24" s="21">
+      <c r="N24">
         <f>AVERAGE(C24:L24)+AVERAGE(C25:L25)</f>
         <v>29.330000000000005</v>
       </c>
-      <c r="O24" s="21">
+      <c r="O24">
         <f>29.33*94.7</f>
         <v>2777.5509999999999</v>
       </c>
@@ -19310,10 +19959,40 @@
       <c r="AL24">
         <v>21.6</v>
       </c>
-    </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM24">
+        <v>15.5</v>
+      </c>
+      <c r="AN24">
+        <v>17.5</v>
+      </c>
+      <c r="AO24">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="AP24">
+        <v>18</v>
+      </c>
+      <c r="AQ24">
+        <v>15</v>
+      </c>
+      <c r="AR24">
+        <v>18.5</v>
+      </c>
+      <c r="AS24">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="AT24">
+        <v>19.7</v>
+      </c>
+      <c r="AU24">
+        <v>17.5</v>
+      </c>
+      <c r="AV24">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -19345,7 +20024,7 @@
       <c r="L25">
         <v>11.6</v>
       </c>
-      <c r="M25" s="21">
+      <c r="M25">
         <f t="shared" si="0"/>
         <v>11.97</v>
       </c>
@@ -19409,10 +20088,40 @@
       <c r="AL25">
         <v>14.3</v>
       </c>
-    </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM25">
+        <v>14.9</v>
+      </c>
+      <c r="AN25">
+        <v>14.1</v>
+      </c>
+      <c r="AO25">
+        <v>13.1</v>
+      </c>
+      <c r="AP25">
+        <v>13.3</v>
+      </c>
+      <c r="AQ25">
+        <v>14.3</v>
+      </c>
+      <c r="AR25">
+        <v>14.1</v>
+      </c>
+      <c r="AS25">
+        <v>10.5</v>
+      </c>
+      <c r="AT25">
+        <v>14.6</v>
+      </c>
+      <c r="AU25">
+        <v>12.9</v>
+      </c>
+      <c r="AV25">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B26">
         <v>58</v>
@@ -19447,15 +20156,15 @@
       <c r="L26">
         <v>19.899999999999999</v>
       </c>
-      <c r="M26" s="21">
+      <c r="M26">
         <f t="shared" si="0"/>
         <v>17.690000000000001</v>
       </c>
-      <c r="N26" s="21">
+      <c r="N26">
         <f>AVERAGE(C26:L26)+AVERAGE(C27:L27)</f>
         <v>31.67</v>
       </c>
-      <c r="O26" s="21">
+      <c r="O26">
         <f>31.67*96.7</f>
         <v>3062.489</v>
       </c>
@@ -19519,10 +20228,40 @@
       <c r="AL26">
         <v>17.2</v>
       </c>
-    </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM26">
+        <v>15.7</v>
+      </c>
+      <c r="AN26">
+        <v>15.5</v>
+      </c>
+      <c r="AO26">
+        <v>18.7</v>
+      </c>
+      <c r="AP26">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="AQ26">
+        <v>14.6</v>
+      </c>
+      <c r="AR26">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="AS26">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="AT26">
+        <v>17</v>
+      </c>
+      <c r="AU26">
+        <v>21.6</v>
+      </c>
+      <c r="AV26">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C27">
         <v>12.5</v>
@@ -19554,7 +20293,7 @@
       <c r="L27">
         <v>14.4</v>
       </c>
-      <c r="M27" s="21">
+      <c r="M27">
         <f t="shared" si="0"/>
         <v>13.979999999999999</v>
       </c>
@@ -19618,10 +20357,40 @@
       <c r="AL27">
         <v>13</v>
       </c>
-    </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM27">
+        <v>12.8</v>
+      </c>
+      <c r="AN27">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="AO27">
+        <v>15.3</v>
+      </c>
+      <c r="AP27">
+        <v>14.7</v>
+      </c>
+      <c r="AQ27">
+        <v>15.4</v>
+      </c>
+      <c r="AR27">
+        <v>14.5</v>
+      </c>
+      <c r="AS27">
+        <v>16.5</v>
+      </c>
+      <c r="AT27">
+        <v>13.9</v>
+      </c>
+      <c r="AU27">
+        <v>13.6</v>
+      </c>
+      <c r="AV27">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B28">
         <v>78</v>
@@ -19656,15 +20425,15 @@
       <c r="L28">
         <v>19</v>
       </c>
-      <c r="M28" s="21">
+      <c r="M28">
         <f t="shared" si="0"/>
         <v>16.600000000000001</v>
       </c>
-      <c r="N28" s="21">
+      <c r="N28">
         <f>AVERAGE(C28:L28)+AVERAGE(C29:L29)</f>
         <v>28.8</v>
       </c>
-      <c r="O28" s="21">
+      <c r="O28">
         <f>28.8*90.6</f>
         <v>2609.2799999999997</v>
       </c>
@@ -19728,10 +20497,40 @@
       <c r="AL28">
         <v>23.2</v>
       </c>
-    </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM28">
+        <v>18.5</v>
+      </c>
+      <c r="AN28">
+        <v>11.8</v>
+      </c>
+      <c r="AO28">
+        <v>22.1</v>
+      </c>
+      <c r="AP28">
+        <v>15</v>
+      </c>
+      <c r="AQ28">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="AR28">
+        <v>17</v>
+      </c>
+      <c r="AS28">
+        <v>21</v>
+      </c>
+      <c r="AT28">
+        <v>10.9</v>
+      </c>
+      <c r="AU28">
+        <v>13.4</v>
+      </c>
+      <c r="AV28">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C29">
         <v>13</v>
@@ -19763,7 +20562,7 @@
       <c r="L29">
         <v>10</v>
       </c>
-      <c r="M29" s="21">
+      <c r="M29">
         <f t="shared" si="0"/>
         <v>12.2</v>
       </c>
@@ -19827,10 +20626,40 @@
       <c r="AL29">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM29">
+        <v>16</v>
+      </c>
+      <c r="AN29">
+        <v>12</v>
+      </c>
+      <c r="AO29">
+        <v>15</v>
+      </c>
+      <c r="AP29">
+        <v>12</v>
+      </c>
+      <c r="AQ29">
+        <v>12</v>
+      </c>
+      <c r="AR29">
+        <v>9</v>
+      </c>
+      <c r="AS29">
+        <v>13</v>
+      </c>
+      <c r="AT29">
+        <v>12</v>
+      </c>
+      <c r="AU29">
+        <v>8</v>
+      </c>
+      <c r="AV29">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B30">
         <v>89</v>
@@ -19865,15 +20694,15 @@
       <c r="L30">
         <v>18.100000000000001</v>
       </c>
-      <c r="M30" s="21">
+      <c r="M30">
         <f t="shared" si="0"/>
         <v>16.149999999999999</v>
       </c>
-      <c r="N30" s="21">
+      <c r="N30">
         <f>AVERAGE(C30:L30)+AVERAGE(C31:L31)</f>
         <v>29.029999999999998</v>
       </c>
-      <c r="O30" s="21">
+      <c r="O30">
         <f>29.03*89.3</f>
         <v>2592.3789999999999</v>
       </c>
@@ -19937,10 +20766,40 @@
       <c r="AL30">
         <v>15.6</v>
       </c>
-    </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM30">
+        <v>14.2</v>
+      </c>
+      <c r="AN30">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="AO30">
+        <v>15.6</v>
+      </c>
+      <c r="AP30">
+        <v>16.7</v>
+      </c>
+      <c r="AQ30">
+        <v>18.2</v>
+      </c>
+      <c r="AR30">
+        <v>16.8</v>
+      </c>
+      <c r="AS30">
+        <v>13.8</v>
+      </c>
+      <c r="AT30">
+        <v>17.3</v>
+      </c>
+      <c r="AU30">
+        <v>15.2</v>
+      </c>
+      <c r="AV30">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C31">
         <v>12.5</v>
@@ -19972,7 +20831,7 @@
       <c r="L31">
         <v>14</v>
       </c>
-      <c r="M31" s="21">
+      <c r="M31">
         <f t="shared" si="0"/>
         <v>12.879999999999999</v>
       </c>
@@ -20036,10 +20895,40 @@
       <c r="AL31">
         <v>14.3</v>
       </c>
-    </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM31">
+        <v>15.4</v>
+      </c>
+      <c r="AN31">
+        <v>15.3</v>
+      </c>
+      <c r="AO31">
+        <v>11.3</v>
+      </c>
+      <c r="AP31">
+        <v>14.5</v>
+      </c>
+      <c r="AQ31">
+        <v>16.5</v>
+      </c>
+      <c r="AR31">
+        <v>13.1</v>
+      </c>
+      <c r="AS31">
+        <v>14.5</v>
+      </c>
+      <c r="AT31">
+        <v>14.6</v>
+      </c>
+      <c r="AU31">
+        <v>14.8</v>
+      </c>
+      <c r="AV31">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B32">
         <v>112</v>
@@ -20074,15 +20963,15 @@
       <c r="L32">
         <v>19.600000000000001</v>
       </c>
-      <c r="M32" s="21">
+      <c r="M32">
         <f t="shared" si="0"/>
         <v>19.380000000000003</v>
       </c>
-      <c r="N32" s="21">
+      <c r="N32">
         <f>AVERAGE(C32:L32)+AVERAGE(C33:L33)</f>
         <v>34.299999999999997</v>
       </c>
-      <c r="O32" s="21">
+      <c r="O32">
         <f>34.3*90.7</f>
         <v>3111.0099999999998</v>
       </c>
@@ -20146,10 +21035,40 @@
       <c r="AL32">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM32">
+        <v>14.5</v>
+      </c>
+      <c r="AN32">
+        <v>15</v>
+      </c>
+      <c r="AO32">
+        <v>17.5</v>
+      </c>
+      <c r="AP32">
+        <v>13.2</v>
+      </c>
+      <c r="AQ32">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="AR32">
+        <v>17.2</v>
+      </c>
+      <c r="AS32">
+        <v>18</v>
+      </c>
+      <c r="AT32">
+        <v>16.3</v>
+      </c>
+      <c r="AU32">
+        <v>17.2</v>
+      </c>
+      <c r="AV32">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C33">
         <v>12</v>
@@ -20181,7 +21100,7 @@
       <c r="L33">
         <v>15.1</v>
       </c>
-      <c r="M33" s="21">
+      <c r="M33">
         <f t="shared" si="0"/>
         <v>14.919999999999998</v>
       </c>
@@ -20244,33 +21163,63 @@
       </c>
       <c r="AL33">
         <v>12.6</v>
+      </c>
+      <c r="AM33">
+        <v>16</v>
+      </c>
+      <c r="AN33">
+        <v>12.7</v>
+      </c>
+      <c r="AO33">
+        <v>14.7</v>
+      </c>
+      <c r="AP33">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="AQ33">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="AR33">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="AS33">
+        <v>12.6</v>
+      </c>
+      <c r="AT33">
+        <v>10.6</v>
+      </c>
+      <c r="AU33">
+        <v>13.3</v>
+      </c>
+      <c r="AV33">
+        <v>12.9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="AC2:AL2"/>
     <mergeCell ref="C2:L2"/>
+    <mergeCell ref="P2:Y2"/>
     <mergeCell ref="C1:Y1"/>
-    <mergeCell ref="P2:Y2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Q135"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C1" s="24"/>
       <c r="D1" s="24"/>
@@ -20282,57 +21231,57 @@
       <c r="J1" s="24"/>
       <c r="K1" s="24"/>
       <c r="L1" s="20" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="O2" s="20" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
